--- a/Krishna_sapkota_S395795/Individual_timesheet_Krishna_S395795_Timesheet.xlsx
+++ b/Krishna_sapkota_S395795/Individual_timesheet_Krishna_S395795_Timesheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krish\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{80E84369-1083-49A5-91F8-8200CF567058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D832E33F-750F-4052-BA1B-C975BD1F83F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="28">
   <si>
     <t>Week</t>
   </si>
@@ -62,13 +62,55 @@
   </si>
   <si>
     <t>Planned the next database and testing activities, including creating sample data, testing CRUD queries and joins, checking constraints, reviewing query performance, and preparing for application-database integration.</t>
+  </si>
+  <si>
+    <t>Week 05</t>
+  </si>
+  <si>
+    <t>Converted the approved OraEarn ER diagram into a relational database design and finalised the tables, attributes, primary keys, foreign keys, and appropriate data types for implementation in Microsoft SQL Server.</t>
+  </si>
+  <si>
+    <t>Created the initial OraEarn database and implemented the main tables using SQL Server Management Studio (SSMS), applying primary-key and foreign-key constraints to maintain relationships between entities.</t>
+  </si>
+  <si>
+    <t>Implemented validation and data-integrity constraints, including NOT NULL, UNIQUE, CHECK, and referential-integrity rules, to ensure that invalid or inconsistent data cannot be inserted into the database.</t>
+  </si>
+  <si>
+    <t>Inserted representative sample data for users, employers, jobs, shifts, breaks, expenses, budgets, savings goals, notifications, and student work-hour monitoring to validate the database structure and relationships.</t>
+  </si>
+  <si>
+    <t>Developed and tested basic SQL CRUD operations for the implemented tables and used SELECT queries and JOIN statements to verify that related information could be retrieved correctly across multiple entities.</t>
+  </si>
+  <si>
+    <t>Reviewed the implemented database against the original requirements and ER design, identified issues in data types, constraints, or relationships, and documented improvements required for the next development stage.</t>
+  </si>
+  <si>
+    <t>Week 06</t>
+  </si>
+  <si>
+    <t>Expanded the OraEarn SQL implementation by developing more complex queries involving multiple tables, JOINs, filtering, grouping, and sorting to support common application requirements and reporting needs.</t>
+  </si>
+  <si>
+    <t>Developed SQL queries for monitoring student work hours, calculating shift and break information, tracking expenses and budgets, and retrieving savings-goal progress from the database.</t>
+  </si>
+  <si>
+    <t>Tested database constraints and relationships using valid and invalid test cases, including duplicate records, missing required values, invalid foreign keys, and incorrect data values, to verify data-integrity rules.</t>
+  </si>
+  <si>
+    <t>Reviewed database query performance and identified frequently accessed columns that may benefit from indexing, while considering how indexes could improve data retrieval without unnecessarily increasing database maintenance overhead.</t>
+  </si>
+  <si>
+    <t>Reviewed database security and access considerations for OraEarn, including appropriate user permissions, protection of sensitive financial information, and the importance of restricting unauthorised INSERT, UPDATE, DELETE, and SELECT operations.</t>
+  </si>
+  <si>
+    <t>Reviewed the completed database implementation with the application requirements and prepared the database for application integration by documenting the schema, important SQL queries, testing results, and remaining improvements for future development.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -80,6 +122,14 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -117,13 +167,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -427,7 +489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -556,7 +618,246 @@
         <v>13</v>
       </c>
     </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="4">
+        <v>1</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="4">
+        <v>1</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="4">
+        <v>1</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="4">
+        <v>1</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>